--- a/notebooks/bench_instances/benchmark_DR_ProxyBatch.xlsx
+++ b/notebooks/bench_instances/benchmark_DR_ProxyBatch.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH9"/>
+  <dimension ref="A1:AH12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1460,6 +1460,324 @@
       </c>
       <c r="AH9" t="n">
         <v>-265329147910198.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DR_ProxyBatch</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>N1950_M1950_T6_seed11_D2.0</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>center_207_Torino_k1950.csv</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>closest_only</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1950</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" t="n">
+        <v>11</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>202830</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.05334122287968442</v>
+      </c>
+      <c r="L10" t="n">
+        <v>11703.13119420402</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="n">
+        <v>3.780669741799997</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>maxTimeLimit</t>
+        </is>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="b">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1377814.022299217</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>3355.913045871374</v>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="n">
+        <v>3355.913045871375</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>900</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>970.2286380000296</v>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>site_swap,local_remove,area_destroy</t>
+        </is>
+      </c>
+      <c r="AC10" t="n">
+        <v>-3355.913045871374</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-335591304587137.4</v>
+      </c>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="n">
+        <v>-3355.913045871375</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-335591304587137.4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DR_ProxyBatch</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>N675_M675_T6_seed11_D2.0</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>center_339_Firenze_k675.csv</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>closest_only</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>675</v>
+      </c>
+      <c r="F11" t="n">
+        <v>675</v>
+      </c>
+      <c r="G11" t="n">
+        <v>6</v>
+      </c>
+      <c r="H11" t="n">
+        <v>11</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>56473</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.1239462277091907</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4052.722635279775</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="n">
+        <v>42.15571366780001</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>maxTimeLimit</t>
+        </is>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="b">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>360932.4870734971</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>2699.089191936292</v>
+      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="n">
+        <v>2699.089191936293</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>900</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>922.9507855999982</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>site_swap,local_remove,area_destroy</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>-2699.089191936292</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-269908919193629.2</v>
+      </c>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="n">
+        <v>-2699.089191936293</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-269908919193629.3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DR_ProxyBatch</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>N675_M675_T6_seed11_D2.0</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>center_339_Firenze_k675.csv</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>closest_only</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>675</v>
+      </c>
+      <c r="F12" t="n">
+        <v>675</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H12" t="n">
+        <v>11</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>56473</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.1239462277091907</v>
+      </c>
+      <c r="L12" t="n">
+        <v>4052.722635279775</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="n">
+        <v>42.15571366780001</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>maxTimeLimit</t>
+        </is>
+      </c>
+      <c r="Q12" t="b">
+        <v>1</v>
+      </c>
+      <c r="R12" t="b">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>360932.4870734971</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>2699.089191936292</v>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="n">
+        <v>2699.089191936293</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>900</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>922.9507855999982</v>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>site_swap,local_remove,area_destroy</t>
+        </is>
+      </c>
+      <c r="AC12" t="n">
+        <v>-2699.089191936292</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-269908919193629.2</v>
+      </c>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="n">
+        <v>-2699.089191936293</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-269908919193629.3</v>
       </c>
     </row>
   </sheetData>
